--- a/output/hmb/ALP-HMB-CASES.xlsx
+++ b/output/hmb/ALP-HMB-CASES.xlsx
@@ -457,7 +457,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>engine hmb v1.1.0 | data a363d729afc29597 | 2026-09-28T03:15:47Z</t>
+          <t>engine hmb v1.1.1 | data a753f3df87285dba | 2026-09-28T14:33:04Z</t>
         </is>
       </c>
     </row>
@@ -1333,7 +1333,7 @@
         <v>0</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E24" s="3" t="n">
         <v>0</v>
@@ -1342,7 +1342,7 @@
         <v>0</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H24" s="3" t="n">
         <v>0</v>
@@ -1354,7 +1354,7 @@
         <v>0</v>
       </c>
       <c r="K24" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1368,7 +1368,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1387,42 +1387,6 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>MIN-NG-100</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>net export 662.4 MW vs DP-OWNR-0051 connection capacity 640 MW (this case)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>SRC-NG-100</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>fuel LHV from the composition (ISO 6976) 47.48 MJ/kg vs DP-CASE-0018 48.4 MJ/kg (-1.90 %)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>WIN-NG-100</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>net export 665.3 MW vs DP-OWNR-0051 connection capacity 640 MW (this case)</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/hmb/ALP-HMB-CASES.xlsx
+++ b/output/hmb/ALP-HMB-CASES.xlsx
@@ -457,7 +457,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>engine hmb v1.1.1 | data a753f3df87285dba | 2026-09-28T14:33:04Z</t>
+          <t>engine hmb v1.1.1 | data 9f2d118f58330dd9 | 2026-09-28T19:00:37Z</t>
         </is>
       </c>
     </row>

--- a/output/hmb/ALP-HMB-CASES.xlsx
+++ b/output/hmb/ALP-HMB-CASES.xlsx
@@ -457,7 +457,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>engine hmb v1.1.1 | data 9f2d118f58330dd9 | 2026-09-28T19:00:37Z</t>
+          <t>engine hmb v1.1.1 | data a6baea26d6584942 | 2026-09-29T02:54:45Z</t>
         </is>
       </c>
     </row>
@@ -909,31 +909,31 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>11.22</v>
+        <v>10.78</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>12.56</v>
+        <v>12.12</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>11.76</v>
+        <v>11.07</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>9.699999999999999</v>
+        <v>9.26</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>12.23</v>
+        <v>11.79</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>10.98</v>
+        <v>10.54</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>8.539999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>11.56</v>
+        <v>11.12</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>12.68</v>
+        <v>12.24</v>
       </c>
     </row>
     <row r="14">
@@ -948,31 +948,31 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>512.85</v>
+        <v>513.29</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>662.36</v>
+        <v>662.8</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>567.11</v>
+        <v>567.8</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>368.1</v>
+        <v>368.54</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>613.5</v>
+        <v>613.9400000000001</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>504.07</v>
+        <v>504.51</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>213.33</v>
+        <v>213.77</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>545.77</v>
+        <v>546.21</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>665.26</v>
+        <v>665.7</v>
       </c>
     </row>
     <row r="15">
@@ -987,29 +987,29 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>83.59</v>
+        <v>83.61</v>
       </c>
       <c r="D15" s="3" t="n">
         <v>107.96</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>92.44</v>
+        <v>92.48</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>60</v>
+        <v>60.03</v>
       </c>
       <c r="G15" s="3" t="n"/>
       <c r="H15" s="3" t="n">
-        <v>82.16</v>
+        <v>82.18000000000001</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>34.77</v>
+        <v>34.82</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>88.95999999999999</v>
+        <v>88.97</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>108.44</v>
+        <v>108.43</v>
       </c>
     </row>
     <row r="16">
@@ -1063,31 +1063,31 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>5835.86</v>
+        <v>5830.85</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>5739.77</v>
+        <v>5735.96</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>6101.83</v>
+        <v>6094.42</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>6201.82</v>
+        <v>6194.41</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>5759.45</v>
+        <v>5755.32</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>5899.53</v>
+        <v>5894.38</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>6956.44</v>
+        <v>6942.12</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>5806.83</v>
+        <v>5802.15</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>5744.26</v>
+        <v>5740.47</v>
       </c>
     </row>
     <row r="18">
@@ -1102,31 +1102,31 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>61.69</v>
+        <v>61.74</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>62.72</v>
+        <v>62.76</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>59</v>
+        <v>59.07</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>58.05</v>
+        <v>58.12</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>62.51</v>
+        <v>62.55</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>61.02</v>
+        <v>61.08</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>51.75</v>
+        <v>51.86</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>62</v>
+        <v>62.05</v>
       </c>
       <c r="K18" s="3" t="n">
-        <v>62.67</v>
+        <v>62.71</v>
       </c>
     </row>
     <row r="19">

--- a/output/hmb/ALP-HMB-CASES.xlsx
+++ b/output/hmb/ALP-HMB-CASES.xlsx
@@ -457,7 +457,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>engine hmb v1.1.1 | data a6baea26d6584942 | 2026-09-29T02:54:45Z</t>
+          <t>engine hmb v1.1.1 | data b6f4b950c7f3b7e0 | 2026-09-29T03:02:22Z</t>
         </is>
       </c>
     </row>
@@ -1024,31 +1024,31 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>831.37</v>
+        <v>832.17</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>1056.05</v>
+        <v>1058.31</v>
       </c>
       <c r="E16" s="3" t="n">
         <v>961.22</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>634.14</v>
+        <v>635.13</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>981.51</v>
+        <v>983.02</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>826.0599999999999</v>
+        <v>827.33</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>412.22</v>
+        <v>412.86</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>880.33</v>
+        <v>881.16</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>1061.51</v>
+        <v>1063.78</v>
       </c>
     </row>
     <row r="17">
@@ -1063,31 +1063,31 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>5830.85</v>
+        <v>5836.42</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>5735.96</v>
+        <v>5748.24</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>6094.42</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>6194.41</v>
+        <v>6204.01</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>5755.32</v>
+        <v>5764.23</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>5894.38</v>
+        <v>5903.5</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>6942.12</v>
+        <v>6952.83</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>5802.15</v>
+        <v>5807.66</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>5740.47</v>
+        <v>5752.77</v>
       </c>
     </row>
     <row r="18">
@@ -1102,31 +1102,31 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>61.74</v>
+        <v>61.68</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>62.76</v>
+        <v>62.63</v>
       </c>
       <c r="E18" s="3" t="n">
         <v>59.07</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>58.12</v>
+        <v>58.03</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>62.55</v>
+        <v>62.45</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>61.08</v>
+        <v>60.98</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>51.86</v>
+        <v>51.78</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>62.05</v>
+        <v>61.99</v>
       </c>
       <c r="K18" s="3" t="n">
-        <v>62.71</v>
+        <v>62.58</v>
       </c>
     </row>
     <row r="19">
@@ -1141,31 +1141,31 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>17.51</v>
+        <v>17.53</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>22.24</v>
+        <v>22.29</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>22.41</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>13.36</v>
+        <v>13.38</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>20.67</v>
+        <v>20.7</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>17.4</v>
+        <v>17.42</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>8.68</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>18.54</v>
+        <v>18.56</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>22.36</v>
+        <v>22.4</v>
       </c>
     </row>
     <row r="20">
@@ -1180,29 +1180,29 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>86054.38</v>
+        <v>86136.46000000001</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>109310.2</v>
+        <v>109544.14</v>
       </c>
       <c r="E20" s="3" t="n"/>
       <c r="F20" s="3" t="n">
-        <v>65639.2</v>
+        <v>65740.92999999999</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>101594.3</v>
+        <v>101751.57</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>85503.95</v>
+        <v>85636.14999999999</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>42668.43</v>
+        <v>42734.28</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>91121.32000000001</v>
+        <v>91207.82000000001</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>109875.38</v>
+        <v>110110.79</v>
       </c>
     </row>
     <row r="21">

--- a/output/hmb/ALP-HMB-CASES.xlsx
+++ b/output/hmb/ALP-HMB-CASES.xlsx
@@ -457,7 +457,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>engine hmb v1.1.1 | data b6f4b950c7f3b7e0 | 2026-09-29T03:02:22Z</t>
+          <t>engine hmb v1.2.0 | data 015d1cd1c6fdda54 | 2026-09-29T03:07:46Z</t>
         </is>
       </c>
     </row>

--- a/output/hmb/ALP-HMB-CASES.xlsx
+++ b/output/hmb/ALP-HMB-CASES.xlsx
@@ -457,7 +457,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>engine hmb v1.2.0 | data 015d1cd1c6fdda54 | 2026-09-29T03:07:46Z</t>
+          <t>engine hmb v1.2.0 | data 6b60fce553593bf5 | 2026-09-29T03:49:51Z</t>
         </is>
       </c>
     </row>
@@ -1333,7 +1333,7 @@
         <v>0</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E24" s="3" t="n">
         <v>0</v>
@@ -1354,7 +1354,7 @@
         <v>0</v>
       </c>
       <c r="K24" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1368,7 +1368,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1387,6 +1387,30 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>MIN-NG-100</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>CW temperature rise 7.20 K vs DP-CASE-0015 &lt;= 7.0 K (Condenser cooling water temperature rise)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>WIN-NG-100</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>CW temperature rise 7.28 K vs DP-CASE-0015 &lt;= 7.0 K (Condenser cooling water temperature rise)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
